--- a/Result/checksun_type/機構樞紐.xlsx
+++ b/Result/checksun_type/機構樞紐.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>1390.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>1444.5</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>1279.0</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>1444.5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1279</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2621809320.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3064445025.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3064445025</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2995037948.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>3354184082.34</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>3354184082.34</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-205381563.4049377</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2621809320</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2621809320.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>1397.0</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>1443.5</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>1271.0</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>1443.5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1271</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>3051965170.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>3278322162.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>3278322162</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>3893845102.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>3342863870.74</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>3342863870.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-168076043.9560924</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>3051965170</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3051965170.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>1410.0</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>1446.25</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>1264.6</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>1446.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1264.6</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2096259385.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3224669751.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3224669751</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>4352192545.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>3315319654.54</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>3315319654.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-154867855.6735959</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2096259385</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2096259385.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>1441.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>1449.25</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>1258.3</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>1449.25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1258.3</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3721364850.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3340911010.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>3340911010</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>4612647385.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>3312666777.28</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>3312666777.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-28070972.03168678</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3721364850</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3721364850.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>1465.0</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>1449.5</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1251.9</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>1449.5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1251.9</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3830826400.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2998318382.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2998318382</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>4521741062.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>3281321399.08</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>3281321399.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-20048474.7921133</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3830826400</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3830826400.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>1474.0</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>1443.25</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>1243.0</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>1443.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1243</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3691195005.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2925630872.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2925630872</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>4423775540.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>3267618992.12</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>3267618992.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-19599770.7072897</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3691195005</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3691195005.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>1484.0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1435.25</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>1233.02</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>1435.25</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1233.02</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2783703115.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>4509368042.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>4509368042</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>4427814102.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>3291495512.14</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>3291495512.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-3298266.453710079</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2783703115</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2783703115.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>1509.0</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1423.5</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1223.18</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>1423.5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1223.18</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>2677465680.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5479715340.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>5479715340</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>4432303790.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>3310041604.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>3310041604.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>117338665.9247503</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>2677465680</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2677465680.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>1497.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>1408.0</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>1211.86</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>1408</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1211.86</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>2008401710.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5884383760.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>5884383760</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4467236355.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>3313437496.2</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>3313437496.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>296869056.4323816</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>2008401710</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2008401710.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>1484.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>1394.25</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>1200.88</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>1394.25</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1200.88</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>3467388850.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6045163742.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6045163742</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4446868730.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>3363750435.9</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>3363750435.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>614424001.9278412</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>3467388850</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>3467388850.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>1477.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>1380.5</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>1189.2</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1189.2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>11609880855.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>5921920209.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>5921920209</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4396772999.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>3345966281.46</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>3345966281.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>889810158.9953613</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>11609880855</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>11609880855.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>23.59</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>25.39</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>25.39</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2967176.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1428504.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1428504.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1130956.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1119787.62</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1119787.62</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>142761.5172408642</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2967176</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2967176.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>23.73</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>24.86</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>25.43</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25.43</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>611036.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>998372.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>998372.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>984557.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1113478.5</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1113478.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-9985.172814279562</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>611036</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>611036.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>23.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>24.97</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>25.49</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>25.49</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>987764.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1002751.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1002751.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>997201.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1136312.96</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1136312.96</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>24605.45470745384</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>987764</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>987764.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>24.15</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>25.1</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>25.55</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>2000588.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>874027.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>874027.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>971902.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1170480.22</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1170480.22</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>32778.15635609266</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2000588</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2000588.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>24.41</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>25.61</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>25.61</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>575958.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>750814.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>750814</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>790451.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1159056.98</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1159056.98</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-65234.06115856941</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>575958</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>575958.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>24.57</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>25.33</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>25.66</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>25.66</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>816517.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>833408.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>833408.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>854893.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1164844.1</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1164844.1</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-50282.79828099487</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>816517</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>816517.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>24.76</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>25.39</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>25.71</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>25.39</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>25.71</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>632932.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>970742.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>970742.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>877555.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1173756.24</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1173756.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-52902.21566013864</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>632932</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>632932.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>24.97</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>25.77</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>25.77</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>344141.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>991651.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>991651</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1042657.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1197554.92</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1197554.92</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-35085.05421391048</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>344141</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>344141.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>25.09</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>25.46</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>25.81</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>25.81</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1384522.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1069777.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1069777.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1118662.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1226904.5</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1226904.5</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>22562.9640740552</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1384522</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1384522.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>25.2</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>25.47</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>25.86</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>25.86</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>988930.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>830089.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>830089.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1028765.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1246738.88</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1246738.88</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-7357.93708863901</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>988930</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>988930.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>25.38</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.48</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>25.89</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>25.89</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1503188.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>876378.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>876378.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1025753.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1303046.38</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1303046.38</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-7454.440996464691</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1503188</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1503188.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>217717</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>149413</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>216732</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>221658</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>301588</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>199194</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>216632</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>357016</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>609988</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>600689</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>797538</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>321219</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>681031</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>86.4</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>90.9</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>97.76</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>97.76000000000001</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>35543.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>22092.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>22092.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>28208.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>40235.04</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>40235.04</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-2154.077054372941</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>35543</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>35543.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>85.24</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>91.35</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>98.08</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>98.08</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>12171.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>21081.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>21081</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>27941.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>41445.9</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>41445.9</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-3440.087832086199</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>12171</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>12171.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>84.98</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>98.55</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>92</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>98.55</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>13855.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>25590.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>25590.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>29151.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>42209.34</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>42209.34</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-2650.242949102059</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>13855</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>13855.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>85.5</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>92.82</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>99.08</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>92.81999999999999</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>99.08</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>28864.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>30541.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>30541.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>30371.6</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>42624.22</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>42624.22</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-1607.670153799638</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>28864</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>28864.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>86.76</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>93.75</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>99.61</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>99.61</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>20028.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>32573.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>32573.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>33052.3</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>42846.94</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>42846.94</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-1668.970797874768</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>20028</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>20028.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>88.16</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>100.1</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>100.1</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>30487.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>34325.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>34325</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>33120.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>44079.5</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>44079.5</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-750.2227609151378</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>30487</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>30487.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>89.92</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>95.34</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>100.71</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>95.34</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>100.71</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>34718.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>34801.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>34801.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>33578.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>45633.44</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>45633.44</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-531.5390380829776</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>34718</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>34718.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>90.85999999999999</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>96.02</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>101.28</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>96.02</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>101.28</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>38610.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>32712.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>32712.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>33839.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>46026.02</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>46026.02</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-653.4716112483657</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>38610</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>38610.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>91.7</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>96.59</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>101.79</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>96.59</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>101.79</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>39024.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>30201.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>30201.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>32603.2</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>47907.58</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>47907.58</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-1221.322729654334</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>39024</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>39024.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>91.94</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>97.02</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>102.33</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>97.02</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>102.33</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>28786.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>33531.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>33531.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>30539.8</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>51238.58</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>51238.58</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-2033.277087032344</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>28786</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>28786.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>92.08</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>97.18</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>102.98</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>102.98</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>32871.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>31916.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>31916.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>31783.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>62063.2</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>62063.2</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-2023.666273035491</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>32871</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>32871.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>182.3</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>193.28</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>216.35</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>193.28</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>216.35</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>1130587314.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>581718075.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>581718075</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>616792931.6</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>988489994.74</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>988489994.74</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-11230341.64629495</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>1130587314</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>1130587314.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>178.3</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>194.12</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>217.1</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>194.12</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>217.1</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>234167162.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>585027434.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>585027434.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>672674941.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>984467164.28</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>984467164.28</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-63428222.48858321</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>234167162</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>234167162.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>178.1</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>195.58</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>218.09</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>195.58</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>218.09</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>474099531.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>606640666.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>606640666.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>712753436.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1006715950.08</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1006715950.08</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-39686313.74583137</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>474099531</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>474099531.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>179.0</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>197.32</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>219.12</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>197.32</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>219.12</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>519891146.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>611197556.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>611197556</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>726341485.2</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1005942036.18</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1005942036.18</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-30058972.44383478</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>519891146</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>519891146.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>181.5</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>198.92</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>220.24</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>198.92</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>220.24</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>549845222.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>625701101.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>625701101.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>712724307.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1005997092.72</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1005997092.72</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-20138337.46084547</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>549845222</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>549845222.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>183.1</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>200.78</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>221.32</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>200.78</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>221.32</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1147134110.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>651867788.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>651867788.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>691822845.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1013207966.72</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1013207966.72</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-8456140.718687654</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1147134110</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1147134110.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>186.8</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>203.42</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>222.49</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>203.42</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>222.49</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>342233322.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>760322447.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>760322447.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>622830477.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1005874676.74</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1005874676.74</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-55460521.20422328</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>342233322</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>342233322.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>190.1</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>205.45</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>223.5</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>205.45</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>223.5</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>496883980.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>818866206.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>818866206.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>640581493.9</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1012914853.74</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1012914853.74</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-34389533.14055181</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>496883980</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>496883980.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>194.1</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>207.18</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>224.43</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>207.18</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>224.43</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>592408873.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>841485414.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>841485414.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>613227877.3</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1031491428.62</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1031491428.62</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-19629637.36600149</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>592408873</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>592408873.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>196.1</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>208.72</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>225.39</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>208.72</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>225.39</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>680678656.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>799747513.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>799747513.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>591479180.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1092446520.98</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1092446520.98</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-8077823.460715294</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>680678656</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>680678656.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>199.4</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>210.32</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>226.9</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>210.32</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>226.9</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>1689407408.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>731777902.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>731777902.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>568004344.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1130358221.32</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1130358221.32</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-744215.2224237919</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>1689407408</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>1689407408.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>39.26000000000001</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>49.56</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>43</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>49.56</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>73021.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>30719.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>30719</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>23237.1</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>60682.16</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>60682.16</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>2417.404453812916</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>73021</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>73021.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>39.09</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>43.41</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>50.05</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>50.05</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>11722.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>20701.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>20701.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>16829.3</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>63080.5</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>63080.5</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-1892.606229439396</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>11722</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>11722.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>39.35</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>43.89</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>50.57</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>50.57</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>23233.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>22940.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>22940.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>17616.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>69727.12</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>69727.12</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-1414.421268748432</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>23233</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>23233.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>39.95</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>51.12</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>51.12</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>22865.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>20807.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>20807.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>17385.9</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>87750.46</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>87750.46000000001</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-1914.106279591761</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>22865</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>22865.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>40.87</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>45.06</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>51.62</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>51.62</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>22754.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>18922.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>18922.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>16823.2</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>94659.74</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>94659.74000000001</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-2520.152499382522</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>22754</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>22754.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>41.86</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>45.66</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>51.98</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>51.98</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>22935.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>15755.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>15755.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>16668.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>97507.38</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>97507.38</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-3284.034509819947</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>22935</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>22935.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>42.85</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>46.29</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>52.34</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>52.34</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>22914.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>12956.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>12956.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>15882.9</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>107347.46</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>107347.46</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-4277.400435094125</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>22914</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>22914.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>43.39</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>46.89</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>52.64</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>12570.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>12293.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>12293.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>15240.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>109728.34</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>109728.34</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-5541.480312803875</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>12570</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>12570.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>43.75</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>47.46</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>52.84</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>52.84</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>13439.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>13964.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>13964.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>15432.5</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>111503.42</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>111503.42</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-6041.112984074807</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>13439</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>13439.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>43.99</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>47.86</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>52.99</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>52.99</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>6918.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>14724.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>14724</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>17222.7</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>115447.12</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>115447.12</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-6632.227050744892</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>6918</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>6918.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>44.0</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>48.15</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>53.14</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>53.14</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>8943.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>17581.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>17581.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>20554.5</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>117215.96</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>117215.96</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-6541.131894175556</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>8943</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>8943.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>66.42</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>67.36</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>68.11</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>68.11</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>42710589.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>23007220.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>23007220.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>35996020.0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>33063664.24</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>33063664.24</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-1007994.177252252</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>42710589</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>42710589.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>65.66</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>67.46</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>68.11</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>68.11</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>22306354.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>23870459.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>23870459.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>34289425.2</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>33106119.9</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>33106119.9</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-2358655.447082456</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>22306354</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>22306354.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>65.34</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>67.65</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>68.15</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>68.15000000000001</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>9540625.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>33864811.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>33864811.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>34750619.0</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>33091816.28</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>33091816.28</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-2017765.816586945</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>9540625</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>9540625.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>65.6</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>67.87</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>68.22</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>68.22</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>24163560.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>41017004.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>41017004.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>36751748.9</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>33804774.0</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>33804774</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-90960.88671524823</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>24163560</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>24163560.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>65.94</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>68.11</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>68.31</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>68.31</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>16314976.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>46288436.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>46288436.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>36703144.1</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>33661523.18</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>33661523.18</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>1098123.151912712</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>16314976</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>16314976.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>66.32000000000001</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>68.28</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>68.39</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>68.39</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>47026782.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>48984819.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>48984819.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>37092188.3</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>34011815.12</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>34011815.12</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>3598515.665955774</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>47026782</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>47026782.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>68.47</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>68.49</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>68.47</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>68.48999999999999</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>72278115.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>44708391.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>44708391</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>35642718.9</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>33787465.26</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>33787465.26</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>3751435.912233166</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>72278115</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>72278115.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>67.62</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>68.57</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>68.56</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>68.56</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>45301591.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>35636426.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>35636426.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>32522117.2</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>32630693.7</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>32630693.7</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>1130413.588621117</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>45301591</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>45301591.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>67.66</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>68.55</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>68.59</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>68.59</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>50520718.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>32486493.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>32486493</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>29256265.9</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>32452622.7</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>32452622.7</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>236065.926724568</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>50520718</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>50520718.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>67.88</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>68.55</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>68.64</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>68.64</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>29796890.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>27117851.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>27117851.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>26134970.2</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>32171582.74</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>32171582.74</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-1609196.694796376</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>29796890</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>29796890.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>68.08</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>68.5</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>68.71</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>68.70999999999999</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>25644641.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>25199557.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>25199557.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>26012652.0</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>32472566.54</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>32472566.54</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-1967404.700726423</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>25644641</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>25644641.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
